--- a/data_derived/figures/source_data/Source_Data_Fig3.xlsx
+++ b/data_derived/figures/source_data/Source_Data_Fig3.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3b_premise" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3c_threshold" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig3d_label_effect" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Literature_audit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -464,7 +465,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Fig3d_label_effect: blocked differences and their normal-approximation 95% intervals, computed by the released code (ncr/analysis.py); unreliable with this few events. The last row is the smallest effect the primary analysis could detect with 80% power.</t>
+          <t>Fig3d_label_effect: blocked differences and their normal-approximation 95% intervals, computed by the released code (ncr/analysis.py); unreliable with this few events. The last row is the smallest effect detectable with 80% power in an approximate normal-theory calculation; it describes the design, not the effects the data exclude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Events are database-matched. Sheet Literature_audit gives the literature check of the four threshold events (three labeled stable, one unstable) and what each source establishes; a sensitivity analysis that counts any earlier experimental report is computed by scripts/literature_sensitivity.py.</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1436,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Smallest reliably detectable effect (80% power), primary analysis</t>
+          <t>Smallest effect detectable with 80% power (approximate, normal theory), primary analysis</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1441,6 +1449,344 @@
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Composition</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Among ten-year cohort realizations</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold side (+/-25 meV/atom, five years)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Earliest matching record</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Record source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Record date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Literature finding</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>What the source establishes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Classification under the outcome definition</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Classification if any earlier experimental report counts</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MgSc2Ru</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OQMD v1.0 (2014)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>mpicsd-mp-1063566</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>MP-ICSD</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>earliest located report after release (2015)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>the 2015 crystal-structure report of Sc2RuMg, an i2 superstructure of the CuAu type, tetragonal rather than the predicted Heusler structure; published within a year of the release; no earlier report found</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Kersting, Rodewald and Poettgen, Z. Kristallogr. 230, 151-155 (2015), doi 10.1515/zkri-2014-1831</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EuNbO3</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OQMD v1.0 (2014)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>cod-1561460</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2016-07-01</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>earlier experimental report</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>samples were synthesized and studied by photoemission by 1998; the source does not establish an earlier experimentally determined crystal structure</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>non-event</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Felser et al., Phys. Rev. B 57, 1510-1514 (1998)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AgAl</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>OQMD v1.0 (2014)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>stable</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>cod-1546733</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>earliest located report after release</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>the zeta precipitate phase, reported in 2017 from electron microscopy with a structural model supported by first-principles calculations; its layered R-3m structure differs from the predicted one; no earlier report found</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Zhang et al., Acta Mater. 132, 525-537 (2017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Li2AgGe</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OQMD v1.0 (2014)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>unstable</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>cod-4341947</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-01</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>earliest located report after release</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>the 2015 structure determination is the earliest report located; no earlier report found</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>unchanged (event)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Henze, Hlukhyy and Faessler, Inorg. Chem. 54, 1152-1158 (2015)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
